--- a/artfynd/A 18951-2023 artfynd.xlsx
+++ b/artfynd/A 18951-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18951-2023 artfynd.xlsx
+++ b/artfynd/A 18951-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94577421</v>
+        <v>94577417</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686924.7062287251</v>
+        <v>686935</v>
       </c>
       <c r="R2" t="n">
-        <v>7095876.802740098</v>
+        <v>7095899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94577417</v>
+        <v>94577418</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1352</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686934.4103955189</v>
+        <v>686931</v>
       </c>
       <c r="R3" t="n">
-        <v>7095898.980216525</v>
+        <v>7095867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,21 +859,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -905,17 +875,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94577418</v>
+        <v>94577422</v>
       </c>
       <c r="B4" t="n">
-        <v>78025</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1352</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686931.0278798474</v>
+        <v>686922</v>
       </c>
       <c r="R4" t="n">
-        <v>7095867.044441259</v>
+        <v>7095891</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,21 +975,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1036,17 +991,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1068,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94577419</v>
+        <v>94577424</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1108,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686923.9583019007</v>
+        <v>686930</v>
       </c>
       <c r="R5" t="n">
-        <v>7095874.554240962</v>
+        <v>7095925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,21 +1091,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,17 +1107,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,37 +1139,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94577422</v>
+        <v>94577421</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1239,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686921.6657043708</v>
+        <v>686925</v>
       </c>
       <c r="R6" t="n">
-        <v>7095890.724202711</v>
+        <v>7095877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,21 +1207,11 @@
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-06-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1298,17 +1223,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1323,6 +1248,122 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94577419</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO Blåbergssjön, Övre Nyland, Bjurholm, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>686924</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7095875</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Per-Anders Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>

--- a/artfynd/A 18951-2023 artfynd.xlsx
+++ b/artfynd/A 18951-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577417</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577418</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577422</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577424</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577421</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,8 +1398,21 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94577419</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>